--- a/data/trans_camb/P6907S1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Edad-trans_camb.xlsx
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 24,48</t>
+          <t>-3,58; 22,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 0,0</t>
+          <t>-9,36; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 0,0</t>
+          <t>-24,83; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 0,0</t>
+          <t>-24,85; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 57,2</t>
+          <t>-9,83; 53,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 0,0</t>
+          <t>-8,98; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 13,95</t>
+          <t>-4,56; 12,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 43,4</t>
+          <t>-4,06; 46,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 2,22</t>
+          <t>-18,63; 2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -1,72</t>
+          <t>-18,93; -2,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 8,06</t>
+          <t>-16,49; 10,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 0,55</t>
+          <t>-20,77; -0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 1,84</t>
+          <t>-18,68; 2,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 12,02</t>
+          <t>-14,38; 11,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -2,72</t>
+          <t>-16,25; -2,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -4,14</t>
+          <t>-16,33; -3,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 5,25</t>
+          <t>-12,77; 5,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 42,15</t>
+          <t>-100,0; 39,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,88; 6,02</t>
+          <t>-92,22; -9,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,59; 88,89</t>
+          <t>-97,64; 115,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,74</t>
+          <t>-100,0; 60,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,32</t>
+          <t>-100,0; 111,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 154,27</t>
+          <t>-79,31; 124,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,28; -14,71</t>
+          <t>-91,29; -6,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,46; -28,21</t>
+          <t>-87,43; -22,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-75,56; 46,25</t>
+          <t>-75,97; 48,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 14,09</t>
+          <t>-5,94; 14,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,76</t>
+          <t>-9,15; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 17,02</t>
+          <t>-0,22; 17,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 4,98</t>
+          <t>-12,88; 5,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; -1,7</t>
+          <t>-15,43; -1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 9,06</t>
+          <t>-8,69; 8,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 7,48</t>
+          <t>-6,37; 6,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -0,87</t>
+          <t>-10,04; -1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 10,39</t>
+          <t>-0,9; 10,86</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 350,65</t>
+          <t>-76,4; 321,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 77,78</t>
+          <t>-90,37; 82,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 423,47</t>
+          <t>-14,8; 437,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 242,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 299,58</t>
+          <t>-63,26; 247,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,06; 153,19</t>
+          <t>-70,2; 128,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,06; -2,41</t>
+          <t>-91,03; -19,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 196,5</t>
+          <t>-14,6; 220,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,29; -3,34</t>
+          <t>-14,82; -3,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 2,61</t>
+          <t>-11,03; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 7,91</t>
+          <t>-7,53; 8,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -3,32</t>
+          <t>-29,61; -3,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -0,84</t>
+          <t>-26,2; -1,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 2,38</t>
+          <t>-22,86; 2,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -4,74</t>
+          <t>-14,33; -4,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -0,55</t>
+          <t>-11,43; -0,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,39</t>
+          <t>-7,97; 3,38</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,9; 81,71</t>
+          <t>-100,0; 104,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,97; 203,1</t>
+          <t>-65,52; 208,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,4; 60,62</t>
+          <t>-87,2; 69,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-90,72; 7,57</t>
+          <t>-92,15; 6,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 60,76</t>
+          <t>-65,21; 67,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 11,81</t>
+          <t>-14,33; 10,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -2,07</t>
+          <t>-18,83; -2,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 16,12</t>
+          <t>-5,37; 15,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 0,0</t>
+          <t>-36,03; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 7,09</t>
+          <t>-28,47; 7,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 11,93</t>
+          <t>-19,22; 12,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 5,05</t>
+          <t>-12,8; 5,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,9; -0,3</t>
+          <t>-14,81; -0,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 11,45</t>
+          <t>-5,88; 11,23</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 608,55</t>
+          <t>-46,16; 542,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 357,33</t>
+          <t>-44,74; 360,38</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,05</t>
+          <t>-8,15; 1,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -2,52</t>
+          <t>-9,37; -2,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,02</t>
+          <t>-2,54; 6,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -2,21</t>
+          <t>-13,33; -2,67</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -3,75</t>
+          <t>-13,36; -4,09</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,75</t>
+          <t>-7,6; 2,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,63</t>
+          <t>-8,81; -1,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -4,08</t>
+          <t>-9,4; -4,12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,34</t>
+          <t>-3,55; 3,33</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 20,46</t>
+          <t>-75,87; 17,28</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-80,42; -29,97</t>
+          <t>-82,47; -29,69</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 106,95</t>
+          <t>-23,83; 92,94</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-92,52; -9,92</t>
+          <t>-100,0; -19,6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-93,29; -43,66</t>
+          <t>-93,2; -45,35</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 35,67</t>
+          <t>-54,89; 31,19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -15,37</t>
+          <t>-77,5; -14,71</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-81,76; -47,87</t>
+          <t>-81,84; -44,51</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 39,87</t>
+          <t>-31,26; 45,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6907S1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,57</t>
+          <t>9,97</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 22,72</t>
+          <t>-3,53; 24,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 0,0</t>
+          <t>-9,52; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 0,0</t>
+          <t>-24,9; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 0,0</t>
+          <t>-28,21; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 53,63</t>
+          <t>-9,93; 44,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 0,0</t>
+          <t>-9,74; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 12,9</t>
+          <t>-4,43; 12,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 46,64</t>
+          <t>-4,19; 40,27</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>254,02%</t>
+          <t>201,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>354,6%</t>
+          <t>240,63%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,59</t>
+          <t>-4,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,04</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,59</t>
+          <t>-4,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 2,28</t>
+          <t>-18,18; 2,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -2,2</t>
+          <t>-18,91; -1,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 10,05</t>
+          <t>-14,43; 12,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -0,23</t>
+          <t>-20,44; 0,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 2,05</t>
+          <t>-19,15; 2,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 11,15</t>
+          <t>-14,31; 10,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -2,3</t>
+          <t>-16,06; -1,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,33; -3,49</t>
+          <t>-15,79; -3,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 5,82</t>
+          <t>-11,63; 8,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-49,69%</t>
+          <t>-31,63%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-21,05%</t>
+          <t>-21,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-37,29%</t>
+          <t>-27,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,85</t>
+          <t>-89,25; 39,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,22; -9,72</t>
+          <t>-91,23; -4,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,64; 115,63</t>
+          <t>-87,16; 125,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 111,42</t>
+          <t>-100,0; 77,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,31; 124,31</t>
+          <t>-77,11; 159,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,29; -6,75</t>
+          <t>-90,79; -2,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,43; -22,54</t>
+          <t>-85,67; -24,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 48,93</t>
+          <t>-68,4; 62,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>3,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 14,49</t>
+          <t>-5,17; 14,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 1,72</t>
+          <t>-9,08; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 17,57</t>
+          <t>-2,02; 14,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 5,67</t>
+          <t>-13,31; 5,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -1,6</t>
+          <t>-16,34; -1,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 8,24</t>
+          <t>-8,94; 8,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 6,89</t>
+          <t>-6,56; 6,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -1,33</t>
+          <t>-9,45; -1,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,86</t>
+          <t>-1,62; 9,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113,69%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 321,91</t>
+          <t>-70,79; 339,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 82,26</t>
+          <t>-91,36; 72,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 437,26</t>
+          <t>-26,74; 332,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 223,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 247,42</t>
+          <t>-65,32; 231,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,2; 128,65</t>
+          <t>-73,66; 117,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-91,03; -19,52</t>
+          <t>-90,71; -10,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 220,13</t>
+          <t>-18,36; 209,69</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>-3,79</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-1,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -3,47</t>
+          <t>-14,88; -3,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 2,19</t>
+          <t>-11,59; 2,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 8,01</t>
+          <t>-7,9; 7,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-29,61; -3,15</t>
+          <t>-25,14; -3,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,2; -1,38</t>
+          <t>-24,78; -0,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 2,34</t>
+          <t>-18,42; 5,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,33; -4,68</t>
+          <t>-15,35; -4,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -0,71</t>
+          <t>-12,09; -0,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 3,38</t>
+          <t>-7,88; 4,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>-1,46%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-53,27%</t>
+          <t>-33,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-24,03%</t>
+          <t>-12,57%</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,42</t>
+          <t>-100,0; 91,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 208,72</t>
+          <t>-69,68; 177,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,2; 69,64</t>
+          <t>-77,32; 168,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-92,15; 6,69</t>
+          <t>-91,24; 23,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 67,32</t>
+          <t>-59,59; 86,33</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>3,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 10,5</t>
+          <t>-12,69; 11,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -2,08</t>
+          <t>-18,62; -2,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 15,59</t>
+          <t>-6,97; 14,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 0,0</t>
+          <t>-39,23; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 7,16</t>
+          <t>-28,73; 7,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 12,75</t>
+          <t>-18,41; 13,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 5,17</t>
+          <t>-12,86; 5,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,81; -0,44</t>
+          <t>-14,9; -0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 11,23</t>
+          <t>-5,09; 10,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 542,9</t>
+          <t>-49,66; 501,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 360,38</t>
+          <t>-40,74; 302,16</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,01</t>
+          <t>-8,19; 1,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -2,5</t>
+          <t>-9,23; -2,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,79</t>
+          <t>-3,06; 6,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,67</t>
+          <t>-12,88; -2,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -4,09</t>
+          <t>-13,14; -3,94</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,37</t>
+          <t>-6,69; 3,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -1,36</t>
+          <t>-8,22; -1,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,12</t>
+          <t>-9,66; -4,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,33</t>
+          <t>-3,55; 3,13</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-24,15%</t>
+          <t>-14,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 17,28</t>
+          <t>-74,98; 30,74</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -29,69</t>
+          <t>-81,96; -27,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 92,94</t>
+          <t>-29,31; 88,61</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,6</t>
+          <t>-93,37; -20,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-93,2; -45,35</t>
+          <t>-92,99; -43,82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 31,19</t>
+          <t>-47,2; 56,9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-77,5; -14,71</t>
+          <t>-76,33; -17,21</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-81,84; -44,51</t>
+          <t>-81,41; -46,05</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 45,57</t>
+          <t>-31,36; 37,43</t>
         </is>
       </c>
     </row>
